--- a/artfynd/A 36120-2024 artfynd.xlsx
+++ b/artfynd/A 36120-2024 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>119796557</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
